--- a/Outputs/Scenarios/PtX_demand_RO_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_RO_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.002484745587897071</v>
       </c>
       <c r="K16" t="n">
-        <v>0.002823900300177805</v>
+        <v>0.003651739830231575</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.0005761261170361109</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00564780060035561</v>
+        <v>0.004609008936288887</v>
       </c>
     </row>
     <row r="20">
@@ -1481,7 +1481,7 @@
         <v>3.580097795272014e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0009413001000592684</v>
+        <v>0.0005761261170361109</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.003678363334053432</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01504512296751427</v>
+        <v>0.0194556708633603</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.003069473902835394</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.03009024593502855</v>
+        <v>0.02455579122268315</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0001935980702133385</v>
       </c>
       <c r="K42" t="n">
-        <v>0.005015040989171425</v>
+        <v>0.003069473902835394</v>
       </c>
     </row>
     <row r="43">
